--- a/data/flight_prices.xlsx
+++ b/data/flight_prices.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Souhrn" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Historie letů'!$A$1:$M$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Historie letů'!$A$1:$M$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2420,8 +2420,2262 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>25533</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Finnair</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>HEL</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>AY 1222, AY 15</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>25567</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>BA 729, AA 107</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>25567</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>BA 729, BA 185</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>25567</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>BA 723, BA 115</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>25783</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>KL 1352, KL 641</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>26194</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Air France</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>CDG</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>AF 1583, AF 4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>26194</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Air France</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>CDG</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>AF 1383, AF 10</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>26830</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>BA 859, AA 101</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>26830</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>BA 859, BA 175</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>26830</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>BA 851, BA 177</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>26830</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>BA 853, BA 183</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>27706</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>KL 1902, KL 641</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>27906</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Aer Lingus</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>DUB</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>EI 643, EI 107</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>28046</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Brussels Airlines</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>BRU</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>SN 502, SN 2547</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>30856</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>KL 1322, KL 641</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>31106</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Finnair</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>HEL</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>AY 1162, AY 15</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>31389</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>DL 46, KL 1323</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>32211</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Aer Lingus</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>DUB</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>EI 104, EI 642</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>34179</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>CPH</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>DL 302, SK 1735</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>34618</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Aer Lingus</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>DUB</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>EI 104, EI 660</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>34821</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>KL 642, KL 1323</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>36340</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Scandinavian Airlines</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>CPH</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>SK 910, SK 1735</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>36340</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Scandinavian Airlines</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>CPH</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>SK 916, SK 1735</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>37655</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tap Air Portugal</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>LIS</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>785</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>TP 202, TP 1270</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>38354</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SWISS</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ZRH</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>LX 17, LX 1370</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>38996</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>OS 36, OS 679</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>46813</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LGA</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Air Canada</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>YYZ</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>AC 8467, AC 934</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>48964</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>DL 305</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>60280</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>DL 304</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>68484</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LGA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Air Canada</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>YYZ</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>AC 935, AC 8470</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>73308</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>OS 38</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>73308</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>OS 36</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>75322</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>OS 37</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:58:17+00:00</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>75322</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>OS 35</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M30"/>
+  <autoFilter ref="A1:M64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2458,7 +4712,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -2478,7 +4732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25220</v>
+        <v>25533</v>
       </c>
     </row>
     <row r="5">
@@ -2489,7 +4743,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-18T12:26:24+00:00</t>
+          <t>2026-09-21T12:58:29+00:00</t>
         </is>
       </c>
     </row>

--- a/data/flight_prices.xlsx
+++ b/data/flight_prices.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Souhrn" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Historie letů'!$A$1:$M$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Historie letů'!$A$1:$M$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4674,8 +4674,1730 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>25542</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Finnair</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2027-06-22</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>HEL</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>AY 1222, AY 15</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>25624</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2027-06-22</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>BA 729, AA 107</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>25624</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2027-06-22</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>BA 729, BA 185</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>25684</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2027-06-22</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>DL 305</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>25768</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2027-06-22</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>KL 1350, DL 47</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>25768</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2027-06-22</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>KL 1354, DL 49</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>25798</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2027-06-22</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>KL 1356, KL 643</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>26206</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Air France</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2027-06-22</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>CDG</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>AF 1583, AF 4</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>26845</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2027-06-22</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>BA 859, BA 175</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>27453</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>BA 180, BA 872</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>27453</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>AA 106, BA 872</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>27945</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Aer Lingus</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2027-06-22</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>DUB</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>EI 643, EI 107</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>28516</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>DL 46, KL 1323</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>28516</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>KL 644, KL 1325</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>29484</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Lufthansa</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>LH 403, LH 1362</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>30759</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2027-06-22</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>KL 1324, DL 49</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>31042</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Aer Lingus</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>DUB</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>EI 104, EI 642</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>31656</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>KL 642, KL 1323</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>33802</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Aer Lingus</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>DUB</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>EI 104, EI 660</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>40764</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Scandinavian Airlines</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>CPH</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>SK 916, SK 1735</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>61742</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>DL 304</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>74879</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>OS 38</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>74879</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>OS 36</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>75090</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LGA</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Air Canada</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>YUL</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>AC 8637, OS 56</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>75157</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>LGA</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2027-06-22</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>YUL</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>OS 55, AC 8640</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:47:41+00:00</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>75484</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2027-06-22</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>OS 37</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M64"/>
+  <autoFilter ref="A1:M90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4712,7 +6434,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
@@ -4732,7 +6454,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25533</v>
+        <v>25542</v>
       </c>
     </row>
     <row r="5">
@@ -4743,7 +6465,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21T12:58:29+00:00</t>
+          <t>2026-09-23T11:47:47+00:00</t>
         </is>
       </c>
     </row>

--- a/data/flight_prices.xlsx
+++ b/data/flight_prices.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Souhrn" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Historie letů'!$A$1:$M$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Historie letů'!$A$1:$M$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6396,8 +6396,2191 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>25568</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>BA 729, BA 185</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>25568</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>BA 723, AA 103</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>25568</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>785</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>BA 723, BA 115</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>25587</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Finnair</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>HEL</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>AY 1222, AY 15</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>26335</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>BA 859, BA 175</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>26335</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>BA 859, AA 107</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>26458</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>DL 305</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>26545</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>KL 1354, DL 49</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>26575</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>KL 1356, KL 643</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>26887</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>BA 861, BA 183</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>27954</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Aer Lingus</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>DUB</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>EI 643, EI 107</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>29783</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Finnair</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>HEL</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>AY 1162, AY 15</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>33041</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>SWISS</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>ZRH</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>LX 17, LX 1370</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>33383</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Aer Lingus</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>DUB</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>EI 104, EI 642</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>33885</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>KL 642, KL 1323</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>33885</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>DL 46, KL 1323</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>33885</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>KL 644, KL 1325</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>35235</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Lufthansa</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>LH 401, LH 1362</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>36886</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Lufthansa</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>MUC</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>LH 413, LH 1622</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>37129</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>OS 36, OS 679</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>38306</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Lufthansa</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>LH 403, LH 1362</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>39176</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Tap Air Portugal</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>LIS</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>785</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>TP 202, TP 1270</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>39589</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Air Serbia</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>BEG</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>JU 501, JU 312</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>41351</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Tap Air Portugal</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>LIS</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>TP 202, TP 1240</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>43624</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Aer Lingus</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>DUB</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>EI 100, EI 642</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>61636</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>LOT</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>LO 2084</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>66114</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>DL 304</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>66626</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LGA</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Air Canada</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>YYZ</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>AC 8467, AC 934</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>74976</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>LGA</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>YUL</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>OS 55, AC 8640</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>75301</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>OS 37</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>75301</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>OS 35</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>79228</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>OS 38</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:57:51+00:00</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>79228</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>OS 36</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M90"/>
+  <autoFilter ref="A1:M123"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6434,7 +8617,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3">
@@ -6454,7 +8637,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25542</v>
+        <v>25568</v>
       </c>
     </row>
     <row r="5">
@@ -6465,7 +8648,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-23T11:47:47+00:00</t>
+          <t>2026-09-25T11:58:03+00:00</t>
         </is>
       </c>
     </row>

--- a/data/flight_prices.xlsx
+++ b/data/flight_prices.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Souhrn" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Historie letů'!$A$1:$M$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Historie letů'!$A$1:$M$150</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M123"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8579,8 +8579,1793 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>25614</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Finnair</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>HEL</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>AY 1222, AY 15</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>25638</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>BA 729, AA 107</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>25864</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Aer Lingus</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>DUB</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>EI 104, EI 660</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>26335</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Aer Lingus</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>DUB</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>EI 104, EI 642</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>26370</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>BA 729, BA 173</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>26488</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>DL 305</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>26574</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>KL 642, KL 1323</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>26574</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>DL 46, KL 1323</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>26574</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>KL 644, KL 1325</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>26914</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>BA 859, AA 101</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>27540</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Lufthansa</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>LH 401, LH 1362</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>27646</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>BA 859, BA 175</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>27646</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>BA 851, BA 189</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>27945</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Aer Lingus</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>DUB</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>EI 643, EI 107</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>29851</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Lufthansa</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>MUC</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>LH 413, LH 1622</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>30089</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>OS 36, OS 679</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>30126</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>BA 723, BA 115</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>31274</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Lufthansa</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>LH 403, LH 1362</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>31729</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>KRK</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>British Airways</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>BA 873, BA 113</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>34319</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Aer Lingus</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>DUB</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>EI 100, EI 660</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>68511</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>LGA</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Air Canada</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>YYZ</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>AC 935, AC 8470</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>74721</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LGA</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Air Canada</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>YUL</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>AC 8637, OS 56</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>75240</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>OS 38</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>75240</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>OS 36</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>75504</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>EWR</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>OS 37</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>OUTBOUND</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>75504</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>VIE</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Austrian</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>OS 35</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-28T14:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>97712</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>PRG</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>DL 304</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Google Flights via SerpApi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M123"/>
+  <autoFilter ref="A1:M150"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8617,7 +10402,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>122</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3">
@@ -8637,7 +10422,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25568</v>
+        <v>25614</v>
       </c>
     </row>
     <row r="5">
@@ -8648,7 +10433,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-25T11:58:03+00:00</t>
+          <t>2026-09-28T14:07:57+00:00</t>
         </is>
       </c>
     </row>
